--- a/data/GI/gastos-ingresos.xlsx
+++ b/data/GI/gastos-ingresos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,1154 @@
         <v>3000</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quincena Gigante</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sueldo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Renta</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Renta</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quincena Gigante</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sueldo</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renta </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pago NU</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Creditos</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>-1835.33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pago NU</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Creditos</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>-3065.99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pago NU</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Creditos</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>-1677.34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pago NU</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Creditos</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>-1273.82</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>81.93000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>235.81</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>42.89</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>229.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>99.42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>89.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>35.16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>66.76000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>91.45999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>58.84</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>37.28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>78.54000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>210.64</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pago Didi</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Creditos</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>-2560.46</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pago Didi</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Creditos</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>-4287.41</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pago Didi</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Creditos</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>-1535.26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pago Didi</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Creditos</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>-2325.43</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Apoyo Tata</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Apoyo Tata</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Apoyo Tata</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Apoyo Tata</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Didi</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>299.61</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Didi</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>886.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Didi</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>642.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Didi</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>201.41</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Didi</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>862.13</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Apoyo Tata</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Apoyo Tata</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Apoyo Tata</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Pago Stori</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Creditos</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>-702.76</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Pago Stori</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Creditos</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pago Stori</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Creditos</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>gasto</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>-602.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/GI/gastos-ingresos.xlsx
+++ b/data/GI/gastos-ingresos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1624,6 +1624,34 @@
         <v>-602.76</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ingreso</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>105.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
